--- a/ig/ch-core/StructureDefinition-ch-core-medicationadministration.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-medicationadministration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="366">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,33 +428,57 @@
     <t>MedicationAdministration.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.extension:indicationCode</t>
+  </si>
+  <si>
+    <t>indicationCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://fhir.ch/ig/ch-core/StructureDefinition/ch-ext-epl-regulated-authorization-limitation-indication-code}
+</t>
+  </si>
+  <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
+    <t>Optional Extension Element - found in all resources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>MedicationAdministration.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -462,6 +486,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -779,6 +806,9 @@
   </si>
   <si>
     <t>MedicationAdministration.performer.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
@@ -1433,12 +1463,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AO44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.1796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.1796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2427,7 +2457,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2446,17 +2476,15 @@
         <v>80</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>80</v>
@@ -2493,16 +2521,14 @@
         <v>80</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>139</v>
@@ -2523,7 +2549,7 @@
         <v>80</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>80</v>
@@ -2540,43 +2566,41 @@
         <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>133</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>80</v>
       </c>
@@ -2624,7 +2648,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2633,7 +2657,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>140</v>
@@ -2656,14 +2680,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2676,24 +2700,26 @@
         <v>80</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O11" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="O11" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P11" t="s" s="2">
         <v>80</v>
       </c>
@@ -2741,7 +2767,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2753,16 +2779,16 @@
         <v>80</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>80</v>
@@ -2796,18 +2822,20 @@
         <v>80</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>80</v>
@@ -2871,13 +2899,13 @@
         <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
@@ -2888,10 +2916,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2914,13 +2942,13 @@
         <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2971,7 +2999,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -2986,10 +3014,10 @@
         <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>80</v>
@@ -3003,10 +3031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3014,32 +3042,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>109</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>80</v>
@@ -3064,13 +3090,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3088,13 +3114,13 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>80</v>
@@ -3103,16 +3129,16 @@
         <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AL14" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>80</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>80</v>
@@ -3120,10 +3146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3131,30 +3157,32 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>80</v>
@@ -3179,13 +3207,13 @@
         <v>80</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>80</v>
@@ -3203,13 +3231,13 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
@@ -3218,16 +3246,16 @@
         <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>183</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -3235,10 +3263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3249,7 +3277,7 @@
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3261,13 +3289,13 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3294,7 +3322,7 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>113</v>
+        <v>188</v>
       </c>
       <c r="Y16" t="s" s="2">
         <v>189</v>
@@ -3318,13 +3346,13 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
@@ -3333,16 +3361,16 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>80</v>
+        <v>193</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>80</v>
@@ -3350,10 +3378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3361,7 +3389,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3373,20 +3401,18 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
         <v>196</v>
       </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3411,7 +3437,7 @@
         <v>80</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>180</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s" s="2">
         <v>197</v>
@@ -3435,10 +3461,10 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3450,16 +3476,16 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AL17" t="s" s="2">
-        <v>200</v>
-      </c>
       <c r="AM17" t="s" s="2">
-        <v>201</v>
+        <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>80</v>
@@ -3467,10 +3493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3493,15 +3519,17 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -3526,13 +3554,13 @@
         <v>80</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>80</v>
+        <v>205</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>80</v>
@@ -3550,7 +3578,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>89</v>
@@ -3593,7 +3621,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3605,7 +3633,7 @@
         <v>80</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
         <v>212</v>
@@ -3668,7 +3696,7 @@
         <v>211</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3711,7 +3739,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>80</v>
@@ -3786,7 +3814,7 @@
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>80</v>
@@ -3795,16 +3823,16 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>223</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>80</v>
@@ -3812,10 +3840,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3823,10 +3851,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -3835,16 +3863,16 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3895,13 +3923,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -3910,16 +3938,16 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>80</v>
@@ -3938,10 +3966,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4013,10 +4041,10 @@
         <v>232</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -4056,7 +4084,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>80</v>
@@ -4065,7 +4093,7 @@
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
         <v>241</v>
@@ -4125,31 +4153,31 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>80</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -4157,21 +4185,21 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>80</v>
@@ -4183,17 +4211,15 @@
         <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -4242,25 +4268,25 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>80</v>
@@ -4274,14 +4300,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4294,26 +4320,24 @@
         <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -4361,7 +4385,7 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4379,7 +4403,7 @@
         <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>80</v>
@@ -4393,42 +4417,46 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
       </c>
@@ -4452,13 +4480,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>258</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -4476,25 +4504,25 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>132</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>80</v>
@@ -4508,10 +4536,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4519,7 +4547,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>89</v>
@@ -4531,16 +4559,16 @@
         <v>80</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4567,13 +4595,13 @@
         <v>80</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>80</v>
+        <v>267</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>80</v>
@@ -4591,10 +4619,10 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>89</v>
@@ -4606,10 +4634,10 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>80</v>
@@ -4623,10 +4651,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4634,10 +4662,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>80</v>
@@ -4646,16 +4674,16 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4682,37 +4710,37 @@
         <v>80</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="AG28" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>80</v>
@@ -4721,16 +4749,16 @@
         <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>80</v>
@@ -4738,10 +4766,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4764,7 +4792,7 @@
         <v>80</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>277</v>
@@ -4772,9 +4800,7 @@
       <c r="M29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>279</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -4799,13 +4825,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
+        <v>188</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>80</v>
+        <v>279</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>280</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -4823,7 +4849,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4838,19 +4864,19 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>283</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
@@ -4869,7 +4895,7 @@
         <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>80</v>
@@ -4946,7 +4972,7 @@
         <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>80</v>
@@ -4961,21 +4987,21 @@
         <v>290</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>80</v>
+        <v>291</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>80</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4986,7 +5012,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>80</v>
@@ -4998,15 +5024,17 @@
         <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5055,13 +5083,13 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
@@ -5070,16 +5098,16 @@
         <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -5087,10 +5115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5113,13 +5141,13 @@
         <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5170,7 +5198,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5185,16 +5213,16 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>80</v>
+        <v>306</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -5202,10 +5230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5216,7 +5244,7 @@
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
@@ -5228,13 +5256,13 @@
         <v>80</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>233</v>
+        <v>308</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5285,25 +5313,25 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>307</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>80</v>
+        <v>311</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>80</v>
@@ -5317,10 +5345,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5346,10 +5374,10 @@
         <v>241</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>242</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>243</v>
+        <v>315</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5400,7 +5428,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5412,13 +5440,13 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>80</v>
+        <v>316</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>245</v>
+        <v>317</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>80</v>
@@ -5432,21 +5460,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>80</v>
@@ -5458,17 +5486,15 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>249</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -5517,25 +5543,25 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>80</v>
@@ -5549,14 +5575,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>250</v>
+        <v>148</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5569,26 +5595,24 @@
         <v>80</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5636,7 +5660,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5654,7 +5678,7 @@
         <v>80</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>132</v>
+        <v>253</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>80</v>
@@ -5668,42 +5692,46 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -5751,25 +5779,25 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>132</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>80</v>
@@ -5783,10 +5811,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5809,17 +5837,15 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -5844,31 +5870,31 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="Z38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5886,13 +5912,13 @@
         <v>80</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>80</v>
@@ -5900,10 +5926,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5926,15 +5952,17 @@
         <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>80</v>
@@ -5959,11 +5987,13 @@
         <v>80</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>188</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>329</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>80</v>
@@ -5981,7 +6011,7 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5999,13 +6029,13 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
@@ -6013,10 +6043,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6039,17 +6069,15 @@
         <v>80</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6078,7 +6106,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -6096,7 +6124,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6114,13 +6142,13 @@
         <v>80</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -6128,10 +6156,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6154,16 +6182,16 @@
         <v>80</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>338</v>
+        <v>185</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6189,13 +6217,11 @@
         <v>80</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>80</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>80</v>
+        <v>343</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -6213,7 +6239,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6231,13 +6257,13 @@
         <v>80</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -6245,10 +6271,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6271,16 +6297,16 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6330,7 +6356,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6348,13 +6374,13 @@
         <v>80</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -6362,10 +6388,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6376,7 +6402,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>80</v>
@@ -6388,16 +6414,16 @@
         <v>80</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6447,13 +6473,13 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>80</v>
@@ -6465,15 +6491,132 @@
         <v>80</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>80</v>
+        <v>359</v>
       </c>
       <c r="AO43" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>80</v>
       </c>
     </row>
